--- a/production/pcbway_bom.xlsx
+++ b/production/pcbway_bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1190,44 +1190,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>J4,J5,J6,J7</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sullins</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PPTC081LFBN-RC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PIN HEADER 1x08 P2.54 VERTICAL (HAND-SOLDER OK)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2.54mm 1x08</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PTH</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
